--- a/Reporte_Labos_2026_FORMATO.xlsx
+++ b/Reporte_Labos_2026_FORMATO.xlsx
@@ -890,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI1000"/>
+  <dimension ref="A1:BI998"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.88" customWidth="1" style="62" min="1" max="1"/>
@@ -1417,12 +1417,16 @@
         <f>P3/N3</f>
         <v/>
       </c>
-      <c r="R3" s="20" t="n"/>
+      <c r="R3" s="20" t="n">
+        <v>172</v>
+      </c>
       <c r="S3" s="21">
         <f>R3/R$37</f>
         <v/>
       </c>
-      <c r="T3" s="22" t="n"/>
+      <c r="T3" s="22" t="n">
+        <v>12728</v>
+      </c>
       <c r="U3" s="23">
         <f>T3/R3</f>
         <v/>
@@ -1779,12 +1783,16 @@
         <f>P5/N5</f>
         <v/>
       </c>
-      <c r="R5" s="20" t="n"/>
+      <c r="R5" s="20" t="n">
+        <v>75325</v>
+      </c>
       <c r="S5" s="21">
         <f>R5/R$37</f>
         <v/>
       </c>
-      <c r="T5" s="22" t="n"/>
+      <c r="T5" s="22" t="n">
+        <v>5574050</v>
+      </c>
       <c r="U5" s="23">
         <f>T5/R5</f>
         <v/>
@@ -1960,12 +1968,16 @@
         <f>P6/N6</f>
         <v/>
       </c>
-      <c r="R6" s="20" t="n"/>
+      <c r="R6" s="20" t="n">
+        <v>518</v>
+      </c>
       <c r="S6" s="21">
         <f>R6/R$37</f>
         <v/>
       </c>
-      <c r="T6" s="22" t="n"/>
+      <c r="T6" s="22" t="n">
+        <v>38332</v>
+      </c>
       <c r="U6" s="23">
         <f>T6/R6</f>
         <v/>
@@ -2141,12 +2153,16 @@
         <f>P7/N7</f>
         <v/>
       </c>
-      <c r="R7" s="20" t="n"/>
+      <c r="R7" s="20" t="n">
+        <v>1708</v>
+      </c>
       <c r="S7" s="21">
         <f>R7/R$37</f>
         <v/>
       </c>
-      <c r="T7" s="22" t="n"/>
+      <c r="T7" s="22" t="n">
+        <v>126392</v>
+      </c>
       <c r="U7" s="23">
         <f>T7/R7</f>
         <v/>
@@ -2499,12 +2515,16 @@
         <f>P9/N9</f>
         <v/>
       </c>
-      <c r="R9" s="20" t="n"/>
+      <c r="R9" s="20" t="n">
+        <v>34604</v>
+      </c>
       <c r="S9" s="21">
         <f>R9/R$37</f>
         <v/>
       </c>
-      <c r="T9" s="22" t="n"/>
+      <c r="T9" s="22" t="n">
+        <v>2560696</v>
+      </c>
       <c r="U9" s="23">
         <f>T9/R9</f>
         <v/>
@@ -2680,12 +2700,16 @@
         <f>P10/N10</f>
         <v/>
       </c>
-      <c r="R10" s="20" t="n"/>
+      <c r="R10" s="20" t="n">
+        <v>28256</v>
+      </c>
       <c r="S10" s="21">
         <f>R10/R$37</f>
         <v/>
       </c>
-      <c r="T10" s="22" t="n"/>
+      <c r="T10" s="22" t="n">
+        <v>2090944</v>
+      </c>
       <c r="U10" s="23">
         <f>T10/R10</f>
         <v/>
@@ -2861,12 +2885,16 @@
         <f>P11/N11</f>
         <v/>
       </c>
-      <c r="R11" s="20" t="n"/>
+      <c r="R11" s="20" t="n">
+        <v>2097</v>
+      </c>
       <c r="S11" s="21">
         <f>R11/R$37</f>
         <v/>
       </c>
-      <c r="T11" s="22" t="n"/>
+      <c r="T11" s="22" t="n">
+        <v>155178</v>
+      </c>
       <c r="U11" s="23">
         <f>T11/R11</f>
         <v/>
@@ -3042,12 +3070,16 @@
         <f>P12/N12</f>
         <v/>
       </c>
-      <c r="R12" s="20" t="n"/>
+      <c r="R12" s="20" t="n">
+        <v>383</v>
+      </c>
       <c r="S12" s="21">
         <f>R12/R$37</f>
         <v/>
       </c>
-      <c r="T12" s="22" t="n"/>
+      <c r="T12" s="22" t="n">
+        <v>28342</v>
+      </c>
       <c r="U12" s="23">
         <f>T12/R12</f>
         <v/>
@@ -3559,12 +3591,16 @@
         <v>444</v>
       </c>
       <c r="Q15" s="23" t="n"/>
-      <c r="R15" s="20" t="n"/>
+      <c r="R15" s="20" t="n">
+        <v>8</v>
+      </c>
       <c r="S15" s="21">
         <f>R15/R$37</f>
         <v/>
       </c>
-      <c r="T15" s="22" t="n"/>
+      <c r="T15" s="22" t="n">
+        <v>592</v>
+      </c>
       <c r="U15" s="23" t="n"/>
       <c r="V15" s="20" t="n">
         <v>8</v>
@@ -4246,12 +4282,16 @@
         <f>P19/N19</f>
         <v/>
       </c>
-      <c r="R19" s="20" t="n"/>
+      <c r="R19" s="20" t="n">
+        <v>274190</v>
+      </c>
       <c r="S19" s="21">
         <f>R19/R$37</f>
         <v/>
       </c>
-      <c r="T19" s="22" t="n"/>
+      <c r="T19" s="22" t="n">
+        <v>20290060</v>
+      </c>
       <c r="U19" s="23">
         <f>T19/R19</f>
         <v/>
@@ -4427,12 +4467,16 @@
         <f>P20/N20</f>
         <v/>
       </c>
-      <c r="R20" s="20" t="n"/>
+      <c r="R20" s="20" t="n">
+        <v>21680</v>
+      </c>
       <c r="S20" s="21">
         <f>R20/R$37</f>
         <v/>
       </c>
-      <c r="T20" s="22" t="n"/>
+      <c r="T20" s="22" t="n">
+        <v>1604320</v>
+      </c>
       <c r="U20" s="23">
         <f>T20/R20</f>
         <v/>
@@ -5117,12 +5161,16 @@
         <f>P24/N24</f>
         <v/>
       </c>
-      <c r="R24" s="20" t="n"/>
+      <c r="R24" s="20" t="n">
+        <v>10088</v>
+      </c>
       <c r="S24" s="21">
         <f>R24/R$37</f>
         <v/>
       </c>
-      <c r="T24" s="22" t="n"/>
+      <c r="T24" s="22" t="n">
+        <v>746512</v>
+      </c>
       <c r="U24" s="23">
         <f>T24/R24</f>
         <v/>
@@ -5298,12 +5346,16 @@
         <f>P25/N25</f>
         <v/>
       </c>
-      <c r="R25" s="20" t="n"/>
+      <c r="R25" s="20" t="n">
+        <v>4609</v>
+      </c>
       <c r="S25" s="21">
         <f>R25/R$37</f>
         <v/>
       </c>
-      <c r="T25" s="22" t="n"/>
+      <c r="T25" s="22" t="n">
+        <v>341066</v>
+      </c>
       <c r="U25" s="23">
         <f>T25/R25</f>
         <v/>
@@ -5479,12 +5531,16 @@
         <f>P26/N26</f>
         <v/>
       </c>
-      <c r="R26" s="20" t="n"/>
+      <c r="R26" s="20" t="n">
+        <v>30701</v>
+      </c>
       <c r="S26" s="21">
         <f>R26/R$37</f>
         <v/>
       </c>
-      <c r="T26" s="22" t="n"/>
+      <c r="T26" s="22" t="n">
+        <v>2271874</v>
+      </c>
       <c r="U26" s="23">
         <f>T26/R26</f>
         <v/>
@@ -5825,12 +5881,16 @@
         <f>P28/N28</f>
         <v/>
       </c>
-      <c r="R28" s="20" t="n"/>
+      <c r="R28" s="20" t="n">
+        <v>9727</v>
+      </c>
       <c r="S28" s="21">
         <f>R28/R$37</f>
         <v/>
       </c>
-      <c r="T28" s="22" t="n"/>
+      <c r="T28" s="22" t="n">
+        <v>719798</v>
+      </c>
       <c r="U28" s="23">
         <f>T28/R28</f>
         <v/>
@@ -6006,12 +6066,16 @@
         <f>P29/N29</f>
         <v/>
       </c>
-      <c r="R29" s="20" t="n"/>
+      <c r="R29" s="20" t="n">
+        <v>29614</v>
+      </c>
       <c r="S29" s="21">
         <f>R29/R$37</f>
         <v/>
       </c>
-      <c r="T29" s="22" t="n"/>
+      <c r="T29" s="22" t="n">
+        <v>2191436</v>
+      </c>
       <c r="U29" s="23">
         <f>T29/R29</f>
         <v/>
@@ -6181,12 +6245,16 @@
         <v>72668</v>
       </c>
       <c r="Q30" s="23" t="n"/>
-      <c r="R30" s="20" t="n"/>
+      <c r="R30" s="20" t="n">
+        <v>804</v>
+      </c>
       <c r="S30" s="21">
         <f>R30/R$37</f>
         <v/>
       </c>
-      <c r="T30" s="22" t="n"/>
+      <c r="T30" s="22" t="n">
+        <v>59496</v>
+      </c>
       <c r="U30" s="23" t="n"/>
       <c r="V30" s="20" t="n">
         <v>2593</v>
@@ -6353,12 +6421,16 @@
         <v>378584</v>
       </c>
       <c r="Q31" s="23" t="n"/>
-      <c r="R31" s="20" t="n"/>
+      <c r="R31" s="20" t="n">
+        <v>6240</v>
+      </c>
       <c r="S31" s="21">
         <f>R31/R$37</f>
         <v/>
       </c>
-      <c r="T31" s="22" t="n"/>
+      <c r="T31" s="22" t="n">
+        <v>461760</v>
+      </c>
       <c r="U31" s="23" t="n"/>
       <c r="V31" s="20" t="n">
         <v>6100</v>
@@ -6525,12 +6597,16 @@
         <v>77922</v>
       </c>
       <c r="Q32" s="23" t="n"/>
-      <c r="R32" s="20" t="n"/>
+      <c r="R32" s="20" t="n">
+        <v>1289</v>
+      </c>
       <c r="S32" s="21">
         <f>R32/R$37</f>
         <v/>
       </c>
-      <c r="T32" s="22" t="n"/>
+      <c r="T32" s="22" t="n">
+        <v>95386</v>
+      </c>
       <c r="U32" s="23" t="n"/>
       <c r="V32" s="20" t="n">
         <v>1462</v>
@@ -6671,12 +6747,16 @@
         <v>888</v>
       </c>
       <c r="Q33" s="23" t="n"/>
-      <c r="R33" s="20" t="n"/>
+      <c r="R33" s="20" t="n">
+        <v>14</v>
+      </c>
       <c r="S33" s="21">
         <f>R33/R$37</f>
         <v/>
       </c>
-      <c r="T33" s="22" t="n"/>
+      <c r="T33" s="22" t="n">
+        <v>1036</v>
+      </c>
       <c r="U33" s="23" t="n"/>
       <c r="V33" s="20" t="n">
         <v>22</v>
@@ -6805,12 +6885,16 @@
         <v>2812</v>
       </c>
       <c r="Q34" s="23" t="n"/>
-      <c r="R34" s="20" t="n"/>
+      <c r="R34" s="20" t="n">
+        <v>46</v>
+      </c>
       <c r="S34" s="21">
         <f>R34/R$37</f>
         <v/>
       </c>
-      <c r="T34" s="22" t="n"/>
+      <c r="T34" s="22" t="n">
+        <v>3404</v>
+      </c>
       <c r="U34" s="23" t="n"/>
       <c r="V34" s="20" t="n">
         <v>107</v>
@@ -6939,12 +7023,16 @@
         <v>1480</v>
       </c>
       <c r="Q35" s="23" t="n"/>
-      <c r="R35" s="20" t="n"/>
+      <c r="R35" s="20" t="n">
+        <v>24</v>
+      </c>
       <c r="S35" s="21">
         <f>R35/R$37</f>
         <v/>
       </c>
-      <c r="T35" s="22" t="n"/>
+      <c r="T35" s="22" t="n">
+        <v>1776</v>
+      </c>
       <c r="U35" s="23" t="n"/>
       <c r="V35" s="20" t="n">
         <v>6</v>
@@ -7073,12 +7161,16 @@
         <v>5920</v>
       </c>
       <c r="Q36" s="23" t="n"/>
-      <c r="R36" s="20" t="n"/>
+      <c r="R36" s="20" t="n">
+        <v>248</v>
+      </c>
       <c r="S36" s="21">
         <f>R36/R$37</f>
         <v/>
       </c>
-      <c r="T36" s="22" t="n"/>
+      <c r="T36" s="22" t="n">
+        <v>18352</v>
+      </c>
       <c r="U36" s="23" t="n"/>
       <c r="V36" s="20" t="n">
         <v>320</v>
@@ -7708,38 +7800,38 @@
       <c r="A43" s="1" t="n">
         <v>5300</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>LAZAR (Fase 1 Startup)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>LAZAR</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr"/>
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>Abono startup; luego % PVP con mínimo</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="0" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="0" t="inlineStr">
         <is>
           <t>STARTUP</t>
         </is>
@@ -7747,7 +7839,7 @@
       <c r="L43" s="72" t="n">
         <v>500000</v>
       </c>
-      <c r="V43" t="n">
+      <c r="V43" s="0" t="n">
         <v>252</v>
       </c>
       <c r="X43" s="72" t="n">
@@ -7774,7 +7866,7 @@
       <c r="AV43" s="47" t="n"/>
       <c r="AW43" s="47" t="n"/>
       <c r="AX43" s="47" t="n"/>
-      <c r="BF43" t="n">
+      <c r="BF43" s="0" t="n">
         <v>252</v>
       </c>
       <c r="BH43" s="72" t="n">
@@ -7786,70 +7878,65 @@
     </row>
     <row r="44" ht="14.25" customHeight="1" s="62">
       <c r="A44" s="1" t="n">
-        <v>5310</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>PROVINCIA ART</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>PROVINCIA ART</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+        <v>5240</v>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>BONOS RAISSE</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>RAISSE</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0,35% sobre monto vendido</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>PRODUCTIVO</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>8166</v>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="inlineStr">
+        <is>
+          <t>SI - DINAMICAS - BONOS</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>Facturado vía Avanter - valor unitario por TRX</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>Trimestral por IPC Indec</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>STARTUP</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>167</v>
       </c>
       <c r="L44" s="72" t="n">
-        <v>1073509.3</v>
+        <v>12358</v>
       </c>
       <c r="M44" s="73" t="n">
-        <v>131.46</v>
-      </c>
-      <c r="R44" t="n">
-        <v>8692</v>
-      </c>
-      <c r="T44" s="72" t="n">
-        <v>1293685.98</v>
-      </c>
-      <c r="U44" s="73" t="n">
-        <v>148.84</v>
-      </c>
-      <c r="V44" t="n">
-        <v>8849</v>
-      </c>
-      <c r="X44" s="72" t="n">
-        <v>1471007.21</v>
-      </c>
-      <c r="Y44" s="73" t="n">
-        <v>166.23</v>
+        <v>74</v>
+      </c>
+      <c r="N44" s="0" t="n">
+        <v>356</v>
+      </c>
+      <c r="P44" s="72" t="n">
+        <v>26344</v>
+      </c>
+      <c r="Q44" s="73" t="n">
+        <v>74</v>
       </c>
       <c r="AD44" s="47" t="n"/>
       <c r="AG44" s="47" t="n"/>
@@ -7869,472 +7956,373 @@
       <c r="AV44" s="47" t="n"/>
       <c r="AW44" s="47" t="n"/>
       <c r="AX44" s="47" t="n"/>
-      <c r="BF44" t="n">
-        <v>25707</v>
+      <c r="BF44" s="0" t="n">
+        <v>523</v>
       </c>
       <c r="BH44" s="72" t="n">
-        <v>3838202.49</v>
+        <v>38702</v>
       </c>
       <c r="BI44" s="73" t="n">
-        <v>149.31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="62">
       <c r="A45" s="1" t="n">
-        <v>5320</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SERDATA (Bonos)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>SERDATA</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+        <v>5250</v>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>BONOS SISCOM (Rayito de Sol)</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>SISCOM</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Valor unitario por bono procesado</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>PRODUCTIVO</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>76676</v>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>SI - DINAMICAS - BONOS</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>Facturado vía Avanter - valor unitario por TRX</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t>Trimestral por IPC Indec</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>STARTUP</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="P45" s="72" t="n">
-        <v>4544586.52</v>
-      </c>
-      <c r="Q45" s="73" t="n">
-        <v>59.27</v>
-      </c>
-      <c r="AD45" s="47" t="n"/>
-      <c r="AG45" s="47" t="n"/>
-      <c r="AH45" s="47" t="n"/>
-      <c r="AI45" s="47" t="n"/>
-      <c r="AJ45" s="47" t="n"/>
-      <c r="AK45" s="47" t="n"/>
-      <c r="AL45" s="47" t="n"/>
-      <c r="AN45" s="47" t="n"/>
-      <c r="AO45" s="47" t="n"/>
-      <c r="AP45" s="47" t="n"/>
-      <c r="AQ45" s="47" t="n"/>
-      <c r="AR45" s="47" t="n"/>
-      <c r="AS45" s="47" t="n"/>
-      <c r="AT45" s="47" t="n"/>
-      <c r="AU45" s="47" t="n"/>
-      <c r="AV45" s="47" t="n"/>
-      <c r="AW45" s="47" t="n"/>
-      <c r="AX45" s="47" t="n"/>
-      <c r="BF45" t="n">
-        <v>76676</v>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="48" t="n"/>
+      <c r="V45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" s="72" t="n">
+        <v>93</v>
+      </c>
+      <c r="Y45" s="73" t="n">
+        <v>93</v>
+      </c>
+      <c r="BF45" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="BH45" s="72" t="n">
-        <v>4544586.52</v>
+        <v>93</v>
       </c>
       <c r="BI45" s="73" t="n">
-        <v>59.27</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="62">
       <c r="A46" s="1" t="n">
-        <v>5240</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>BONOS RAISSE</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>RAISSE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+        <v>5260</v>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>BONOS ENA (alta 22/04/2026)</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>SI - DINAMICAS - BONOS</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Facturado vía Avanter - valor unitario por TRX</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Trimestral por IPC Indec</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr"/>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>Alta laboratorio nuevo - Avanter</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
         <is>
           <t>STARTUP</t>
         </is>
       </c>
-      <c r="J46" t="n">
-        <v>167</v>
-      </c>
-      <c r="L46" s="72" t="n">
-        <v>12358</v>
-      </c>
-      <c r="M46" s="73" t="n">
-        <v>74</v>
-      </c>
-      <c r="N46" t="n">
-        <v>356</v>
-      </c>
-      <c r="P46" s="72" t="n">
-        <v>26344</v>
-      </c>
-      <c r="Q46" s="73" t="n">
-        <v>74</v>
-      </c>
-      <c r="AD46" s="47" t="n"/>
-      <c r="AG46" s="47" t="n"/>
-      <c r="AH46" s="47" t="n"/>
-      <c r="AI46" s="47" t="n"/>
-      <c r="AJ46" s="47" t="n"/>
-      <c r="AK46" s="47" t="n"/>
-      <c r="AL46" s="47" t="n"/>
-      <c r="AN46" s="47" t="n"/>
-      <c r="AO46" s="47" t="n"/>
-      <c r="AP46" s="47" t="n"/>
-      <c r="AQ46" s="47" t="n"/>
-      <c r="AR46" s="47" t="n"/>
-      <c r="AS46" s="47" t="n"/>
-      <c r="AT46" s="47" t="n"/>
-      <c r="AU46" s="47" t="n"/>
-      <c r="AV46" s="47" t="n"/>
-      <c r="AW46" s="47" t="n"/>
-      <c r="AX46" s="47" t="n"/>
-      <c r="BF46" t="n">
-        <v>523</v>
+      <c r="Q46" s="48" t="n"/>
+      <c r="X46" s="72" t="n">
+        <v>547420.8</v>
       </c>
       <c r="BH46" s="72" t="n">
-        <v>38702</v>
-      </c>
-      <c r="BI46" s="73" t="n">
-        <v>74</v>
+        <v>547420.8</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="62">
       <c r="A47" s="1" t="n">
-        <v>5250</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>BONOS SISCOM (Rayito de Sol)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>SISCOM</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+        <v>5270</v>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>BONOS CONVATEC (alta 24/04/2026)</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>CONVATEC</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>SI - DINAMICAS - BONOS</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Facturado vía Avanter - valor unitario por TRX</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Trimestral por IPC Indec</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr"/>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>Alta laboratorio nuevo - Avanter</t>
+        </is>
+      </c>
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="I47" s="0" t="inlineStr">
         <is>
           <t>STARTUP</t>
         </is>
       </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="72" t="n">
-        <v>0</v>
-      </c>
       <c r="Q47" s="48" t="n"/>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
       <c r="X47" s="72" t="n">
-        <v>93</v>
-      </c>
-      <c r="Y47" s="73" t="n">
-        <v>93</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>1</v>
+        <v>547420.8</v>
       </c>
       <c r="BH47" s="72" t="n">
-        <v>93</v>
-      </c>
-      <c r="BI47" s="73" t="n">
-        <v>93</v>
+        <v>547420.8</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="62">
       <c r="A48" s="1" t="n">
-        <v>5260</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>BONOS ENA (alta 22/04/2026)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ENA</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+        <v>5220</v>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>BONOS MEGALABS</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>MEGALABS</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Alta laboratorio nuevo - Avanter</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>SI - DINAMICAS - BONOS</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>Facturado vía Avanter</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t>Trimestral por IPC Indec</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
         <is>
           <t>STARTUP</t>
         </is>
       </c>
+      <c r="J48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q48" s="48" t="n"/>
-      <c r="X48" s="72" t="n">
-        <v>547420.8</v>
-      </c>
-      <c r="BH48" s="72" t="n">
-        <v>547420.8</v>
-      </c>
     </row>
     <row r="49" ht="14.25" customHeight="1" s="62">
       <c r="A49" s="1" t="n">
-        <v>5270</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>BONOS CONVATEC (alta 24/04/2026)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CONVATEC</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+        <v>5230</v>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>BONOS SIEGFRIED</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>SIEGFRIED</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Alta laboratorio nuevo - Avanter</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t>SI - DINAMICAS - BONOS</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>Facturado vía Avanter</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t>Trimestral por IPC Indec</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
         <is>
           <t>STARTUP</t>
         </is>
       </c>
+      <c r="J49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" s="48" t="n"/>
-      <c r="X49" s="72" t="n">
-        <v>547420.8</v>
-      </c>
-      <c r="BH49" s="72" t="n">
-        <v>547420.8</v>
-      </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="62">
-      <c r="A50" s="1" t="n">
-        <v>5220</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>BONOS MEGALABS</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>MEGALABS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>5120</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>BONOS CEODERMA - VIA AVANTER (solo enero)</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>CEODERMA</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>SI - DINAMICAS - BONOS</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Facturado vía Avanter</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t>SI - ETICOS</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>Facturado vía Avanter - valor unitario por TRX</t>
+        </is>
+      </c>
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>Trimestral por IPC Indec</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>STARTUP</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>PRODUCTIVO</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>355</v>
       </c>
       <c r="L50" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="72" t="n">
-        <v>0</v>
+        <v>26270</v>
+      </c>
+      <c r="M50" s="73" t="n">
+        <v>74</v>
       </c>
       <c r="Q50" s="48" t="n"/>
+      <c r="BF50" s="0" t="n">
+        <v>355</v>
+      </c>
+      <c r="BH50" s="72" t="n">
+        <v>26270</v>
+      </c>
+      <c r="BI50" s="73" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="62">
-      <c r="A51" s="1" t="n">
-        <v>5230</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>BONOS SIEGFRIED</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>SIEGFRIED</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>SI - DINAMICAS - BONOS</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Facturado vía Avanter</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Trimestral por IPC Indec</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>STARTUP</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="72" t="n">
-        <v>0</v>
-      </c>
+      <c r="A51" s="1" t="n"/>
       <c r="Q51" s="48" t="n"/>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="62">
       <c r="A52" s="1" t="n"/>
-      <c r="Q52" s="48" t="n"/>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="62">
       <c r="A53" s="1" t="n"/>
-      <c r="Q53" s="48" t="n"/>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="62">
       <c r="A54" s="1" t="n"/>
@@ -11171,12 +11159,8 @@
     <row r="998" ht="14.25" customHeight="1" s="62">
       <c r="A998" s="1" t="n"/>
     </row>
-    <row r="999" ht="14.25" customHeight="1" s="62">
-      <c r="A999" s="1" t="n"/>
-    </row>
-    <row r="1000" ht="14.25" customHeight="1" s="62">
-      <c r="A1000" s="1" t="n"/>
-    </row>
+    <row r="999" ht="14.25" customHeight="1" s="62"/>
+    <row r="1000" ht="14.25" customHeight="1" s="62"/>
   </sheetData>
   <autoFilter ref="$A$2:$BG$41"/>
   <mergeCells count="18">
